--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,57 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -496,36 +486,32 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -534,18 +520,20 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
@@ -557,12 +545,6 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -572,21 +554,23 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -595,12 +579,6 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -637,12 +615,6 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -650,12 +622,14 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -664,21 +638,15 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -688,15 +656,17 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -705,19 +675,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -726,15 +690,17 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -746,16 +712,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -764,36 +724,32 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -802,9 +758,11 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -816,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -825,12 +783,6 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -840,36 +792,32 @@
           <t>其他右下上櫃</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +826,9 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -901,12 +851,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -916,7 +860,9 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
@@ -930,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -939,12 +885,6 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,36 +894,32 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -992,9 +928,11 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -1003,10 +941,10 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1015,13 +953,7 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1057,12 +989,6 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1077,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1095,12 +1021,6 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1110,9 +1030,11 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1121,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1133,12 +1055,6 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1148,9 +1064,11 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1159,24 +1077,18 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1186,36 +1098,32 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
       <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
         <v>4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1224,15 +1132,17 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1247,12 +1157,6 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1262,7 +1166,9 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1285,12 +1191,6 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1309,24 +1209,22 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1336,7 +1234,9 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1353,19 +1253,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1374,7 +1268,9 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
@@ -1388,22 +1284,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1412,36 +1302,32 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
       </c>
       <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
         <v>6</v>
       </c>
-      <c r="H26" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
       <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1450,36 +1336,32 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>14</v>
+      </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="n">
-        <v>17</v>
-      </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>13</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -1489,10 +1371,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1504,21 +1386,15 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1529,7 +1405,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1538,28 +1414,22 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1568,18 +1438,20 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1591,12 +1463,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1606,15 +1472,17 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -1623,18 +1491,12 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1644,12 +1506,14 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1664,15 +1528,9 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1682,12 +1540,14 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1705,12 +1565,6 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1720,12 +1574,14 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1743,12 +1599,6 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1758,7 +1608,9 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1774,18 +1626,14 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1794,46 +1642,30 @@
           <t>塑膠工業平上櫃</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上市</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>居家生活右上上櫃</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
@@ -1843,30 +1675,28 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>居家生活右下上市</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1889,22 +1719,18 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>居家生活右下上櫃</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1924,22 +1750,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
+          <t>居家生活平上市</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1961,56 +1781,58 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>居家生活平上櫃</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>建材營造右上上市</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -2033,22 +1855,18 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>建材營造右上上櫃</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
@@ -2068,25 +1886,21 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -2103,30 +1917,26 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>建材營造右下上櫃</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2148,28 +1958,22 @@
       </c>
       <c r="J45" t="n">
         <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
+          <t>建材營造平上市</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2181,28 +1985,24 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>建材營造平上櫃</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2225,27 +2025,23 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>數位雲端右上上市</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2263,22 +2059,18 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>數位雲端右上上櫃</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2286,42 +2078,38 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2330,31 +2118,27 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>數位雲端右下上櫃</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2362,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2371,28 +2155,24 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
@@ -2400,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2415,22 +2195,18 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>數位雲端平上櫃</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
@@ -2441,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2453,31 +2229,19 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
         <v>0</v>
       </c>
@@ -2491,22 +2255,18 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2514,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2529,19 +2289,13 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2569,22 +2323,18 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>橡膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2592,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2607,27 +2357,23 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>橡膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2645,31 +2391,25 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>橡膠工業平上市</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>0</v>
       </c>
@@ -2683,28 +2423,18 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
+          <t>水泥工業右上上市</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>0</v>
       </c>
@@ -2720,11 +2450,7 @@
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
+      <c r="J60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2734,7 +2460,9 @@
           <t>水泥工業右下上市</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
@@ -2757,12 +2485,6 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2772,21 +2494,27 @@
           <t>水泥工業平上市</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2796,12 +2524,14 @@
           <t>汽車工業右上上市</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -2810,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2820,12 +2550,6 @@
       </c>
       <c r="J63" t="n">
         <v>1</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2834,9 +2558,11 @@
           <t>汽車工業右下上市</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2851,18 +2577,12 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2872,9 +2592,11 @@
           <t>汽車工業平上市</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2895,12 +2617,6 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2910,35 +2626,31 @@
           <t>油電燃氣業右上上市</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2948,7 +2660,9 @@
           <t>油電燃氣業右下上市</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -2971,12 +2685,6 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2986,7 +2694,9 @@
           <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -3009,12 +2719,6 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3024,40 +2728,48 @@
           <t>油電燃氣業平上市</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
       <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>油電燃氣業平上櫃</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -3072,25 +2784,21 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
@@ -3101,134 +2809,134 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
+          <t>玻璃陶瓷右下上市</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>生技醫療業右上上市</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>3</v>
-      </c>
-      <c r="L74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
+          <t>生技醫療業右上上櫃</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3237,50 +2945,44 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3289,30 +2991,26 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>2</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -3321,42 +3019,38 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3365,27 +3059,23 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3403,22 +3093,18 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
-      </c>
-      <c r="K79" t="n">
-        <v>5</v>
-      </c>
-      <c r="L79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
@@ -3441,24 +3127,20 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3479,27 +3161,23 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3517,27 +3195,23 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3555,22 +3229,18 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3586,27 +3256,25 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
@@ -3614,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3623,28 +3291,24 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
@@ -3667,27 +3331,23 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -3696,31 +3356,27 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -3734,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3743,22 +3399,18 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
@@ -3775,30 +3427,26 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -3816,75 +3464,79 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -3919,12 +3571,6 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -3959,12 +3605,6 @@
       <c r="J94" t="n">
         <v>0</v>
       </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -3972,12 +3612,14 @@
           <t>航運業平上市</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -3995,12 +3637,6 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4010,7 +3646,9 @@
           <t>航運業平上櫃</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -4020,27 +3658,11 @@
       <c r="E96" t="n">
         <v>0</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -4048,12 +3670,14 @@
           <t>觀光事業右上上市</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -4071,12 +3695,6 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4086,7 +3704,9 @@
           <t>觀光事業右上上櫃</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
@@ -4109,12 +3729,6 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4151,12 +3765,6 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -4164,7 +3772,9 @@
           <t>觀光事業右下上櫃</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -4188,12 +3798,6 @@
       </c>
       <c r="J100" t="n">
         <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -4202,7 +3806,9 @@
           <t>觀光事業平上市</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
@@ -4222,13 +3828,7 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4236,7 +3836,9 @@
           <t>觀光事業平上櫃</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
@@ -4244,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -4259,12 +3861,6 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4274,12 +3870,14 @@
           <t>貿易百貨右上上市</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -4294,16 +3892,10 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
-      </c>
-      <c r="K103" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4313,13 +3905,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -4337,12 +3929,6 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4352,7 +3938,9 @@
           <t>貿易百貨平上市</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
@@ -4369,18 +3957,12 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4390,7 +3972,9 @@
           <t>資訊服務業右上上市</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>3</v>
+      </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
@@ -4413,12 +3997,6 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4428,18 +4006,20 @@
           <t>資訊服務業右上上櫃</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4448,16 +4028,10 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -4466,9 +4040,11 @@
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4489,12 +4065,6 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4508,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -4529,12 +4099,6 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4544,12 +4108,14 @@
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -4567,12 +4133,6 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4582,9 +4142,11 @@
           <t>資訊服務業平上櫃</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4599,30 +4161,26 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -4643,24 +4201,24 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平上櫃</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
@@ -4677,12 +4235,6 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4692,36 +4244,32 @@
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -4730,12 +4278,14 @@
           <t>通信網路業右上上櫃</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -4744,22 +4294,16 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -4769,10 +4313,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -4787,18 +4331,12 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
         <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4809,36 +4347,30 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4848,9 +4380,11 @@
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -4871,13 +4405,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -4886,15 +4414,17 @@
           <t>通信網路業平上櫃</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -4910,12 +4440,6 @@
       </c>
       <c r="J119" t="n">
         <v>1</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -4924,7 +4448,9 @@
           <t>造紙工業右上上市</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
@@ -4947,12 +4473,6 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4989,12 +4509,6 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -5002,19 +4516,33 @@
           <t>造紙工業平上市</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -5022,7 +4550,9 @@
           <t>運動休閒右上上市</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
@@ -5046,12 +4576,6 @@
       </c>
       <c r="J123" t="n">
         <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -5060,15 +4584,17 @@
           <t>運動休閒右上上櫃</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -5083,12 +4609,6 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5098,12 +4618,14 @@
           <t>運動休閒右下上市</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5118,15 +4640,9 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5136,12 +4652,14 @@
           <t>運動休閒右下上櫃</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5150,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5160,12 +4678,6 @@
       </c>
       <c r="J126" t="n">
         <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -5174,7 +4686,9 @@
           <t>運動休閒平上市</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -5198,12 +4712,6 @@
       </c>
       <c r="J127" t="n">
         <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -5212,7 +4720,9 @@
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
@@ -5235,12 +4745,6 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5250,9 +4754,11 @@
           <t>金融保險右上上市</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -5273,12 +4779,6 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5303,16 +4803,16 @@
       <c r="F130" t="n">
         <v>0</v>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
       <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5322,7 +4822,9 @@
           <t>金融保險平上市</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
@@ -5345,12 +4847,6 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5360,12 +4856,14 @@
           <t>金融業右上上櫃</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -5377,18 +4875,12 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5398,7 +4890,9 @@
           <t>金融業右下上櫃</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
@@ -5421,12 +4915,6 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5436,21 +4924,31 @@
           <t>金融業平上櫃</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
       <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5460,7 +4958,9 @@
           <t>鋼鐵工業右上上市</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
@@ -5468,28 +4968,22 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -5498,9 +4992,11 @@
           <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -5512,22 +5008,16 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -5563,12 +5053,6 @@
       <c r="J137" t="n">
         <v>0</v>
       </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -5576,7 +5060,9 @@
           <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
@@ -5587,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5599,12 +5085,6 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5614,7 +5094,9 @@
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
@@ -5637,12 +5119,6 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5652,7 +5128,9 @@
           <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -5675,13 +5153,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -5690,35 +5162,31 @@
           <t>電器電纜右上上市</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5728,21 +5196,23 @@
           <t>電器電纜右上上櫃</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -5751,12 +5221,6 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5766,7 +5230,9 @@
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
@@ -5789,12 +5255,6 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5804,7 +5264,9 @@
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
@@ -5827,12 +5289,6 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5842,9 +5298,11 @@
           <t>電子通路業右上上市</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -5853,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5862,15 +5320,9 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
-      </c>
-      <c r="K145" t="n">
-        <v>3</v>
-      </c>
-      <c r="L145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5880,7 +5332,9 @@
           <t>電子通路業右上上櫃</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
@@ -5888,27 +5342,21 @@
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5918,7 +5366,9 @@
           <t>電子通路業右下上市</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
@@ -5941,12 +5391,6 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5963,10 +5407,10 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5981,12 +5425,6 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5996,7 +5434,9 @@
           <t>電子通路業平上市</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
@@ -6019,12 +5459,6 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6034,8 +5468,12 @@
           <t>電子通路業平上櫃</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
       <c r="D150" t="n">
         <v>0</v>
       </c>
@@ -6055,12 +5493,6 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6070,36 +5502,32 @@
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>7</v>
+      </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D151" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G151" t="n">
         <v>5</v>
       </c>
       <c r="H151" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
-      </c>
-      <c r="K151" t="n">
-        <v>12</v>
-      </c>
-      <c r="L151" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -6108,36 +5536,32 @@
           <t>電子零組件業右上上櫃</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="n">
+        <v>7</v>
+      </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" t="n">
+        <v>9</v>
+      </c>
+      <c r="G152" t="n">
         <v>6</v>
       </c>
-      <c r="E152" t="n">
-        <v>3</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>2</v>
-      </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
-      </c>
-      <c r="K152" t="n">
         <v>5</v>
-      </c>
-      <c r="L152" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -6147,36 +5571,30 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6190,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
@@ -6202,21 +5620,15 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6226,18 +5638,20 @@
           <t>電子零組件業平上市</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -6246,15 +5660,9 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6264,36 +5672,32 @@
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
       <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="n">
         <v>2</v>
       </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>1</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
       <c r="H156" t="n">
         <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -6302,36 +5706,32 @@
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -6340,36 +5740,32 @@
           <t>電機機械右上上櫃</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
       <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>3</v>
       </c>
-      <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
-      </c>
-      <c r="K158" t="n">
-        <v>3</v>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -6378,7 +5774,9 @@
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
@@ -6401,13 +5799,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -6417,10 +5809,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -6441,12 +5833,6 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6456,9 +5842,11 @@
           <t>電機機械平上市</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -6479,12 +5867,6 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6494,7 +5876,9 @@
           <t>電機機械平上櫃</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
@@ -6502,10 +5886,10 @@
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -6514,15 +5898,9 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6532,36 +5910,32 @@
           <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
         <v>2</v>
       </c>
-      <c r="E163" t="n">
-        <v>5</v>
-      </c>
-      <c r="F163" t="n">
-        <v>2</v>
-      </c>
-      <c r="G163" t="n">
-        <v>2</v>
-      </c>
-      <c r="H163" t="n">
-        <v>1</v>
-      </c>
-      <c r="I163" t="n">
-        <v>4</v>
-      </c>
       <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -6570,15 +5944,17 @@
           <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>2</v>
+      </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
@@ -6587,19 +5963,13 @@
         <v>3</v>
       </c>
       <c r="H164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
-      </c>
-      <c r="K164" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -6608,15 +5978,17 @@
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -6625,18 +5997,12 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6646,9 +6012,11 @@
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -6657,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -6669,12 +6037,6 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="n">
-        <v>1</v>
-      </c>
-      <c r="L166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6684,9 +6046,11 @@
           <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -6701,18 +6065,12 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6722,21 +6080,23 @@
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -6746,12 +6106,6 @@
       </c>
       <c r="J168" t="n">
         <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -6760,7 +6114,9 @@
           <t>食品工業右上上市</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
@@ -6784,12 +6140,6 @@
       </c>
       <c r="J169" t="n">
         <v>0</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -6798,7 +6148,9 @@
           <t>食品工業右上上櫃</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
@@ -6821,12 +6173,6 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6836,7 +6182,9 @@
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="n">
+        <v>0</v>
+      </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
@@ -6859,12 +6207,6 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6874,7 +6216,9 @@
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
@@ -6885,10 +6229,10 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -6897,12 +6241,6 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6912,7 +6250,9 @@
           <t>食品工業平上市</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
@@ -6920,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -6935,12 +6275,6 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6950,7 +6284,9 @@
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
@@ -6969,10 +6305,12 @@
       <c r="H174" t="n">
         <v>0</v>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -5506,13 +5506,13 @@
         <v>7</v>
       </c>
       <c r="C151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D151" t="n">
         <v>3</v>
       </c>
       <c r="E151" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F151" t="n">
         <v>3</v>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C152" t="n">
         <v>3</v>
@@ -5549,13 +5549,13 @@
         <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G152" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H152" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I152" t="n">
         <v>11</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -486,14 +491,12 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>9</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -502,7 +505,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>10</v>
@@ -513,6 +516,9 @@
       <c r="J2" t="n">
         <v>2</v>
       </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -520,17 +526,15 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -539,7 +543,7 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -547,6 +551,9 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -554,11 +561,9 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -570,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -579,6 +584,9 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -592,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -613,6 +621,9 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -622,14 +633,12 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -647,6 +656,9 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -656,17 +668,15 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -675,12 +685,15 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -690,9 +703,7 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>1</v>
       </c>
@@ -706,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -715,6 +726,9 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -724,9 +738,7 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>1</v>
       </c>
@@ -751,6 +763,9 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -758,9 +773,7 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>1</v>
       </c>
@@ -783,6 +796,9 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -819,6 +835,9 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -826,9 +845,7 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -842,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -851,6 +868,9 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -860,9 +880,7 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
@@ -876,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -886,6 +904,9 @@
       </c>
       <c r="J13" t="n">
         <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -894,9 +915,7 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
@@ -921,6 +940,9 @@
       <c r="J14" t="n">
         <v>2</v>
       </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -928,26 +950,24 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -955,6 +975,9 @@
       <c r="J15" t="n">
         <v>3</v>
       </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -962,9 +985,7 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
@@ -987,6 +1008,9 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1023,6 +1047,9 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1030,9 +1057,7 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -1055,6 +1080,9 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1064,31 +1092,32 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,9 +1127,7 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>1</v>
       </c>
@@ -1117,12 +1144,15 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1132,9 +1162,7 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1148,16 +1176,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1166,9 +1197,7 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1191,6 +1220,9 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1200,9 +1232,7 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
@@ -1216,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1225,6 +1255,9 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1234,9 +1267,7 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1253,13 +1284,16 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1268,9 +1302,7 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
@@ -1287,13 +1319,16 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1302,14 +1337,12 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>10</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -1329,6 +1362,9 @@
       <c r="J26" t="n">
         <v>4</v>
       </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1336,9 +1372,7 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>14</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>3</v>
       </c>
@@ -1346,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -1355,14 +1389,17 @@
         <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
         <v>9</v>
       </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1370,9 +1407,7 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>2</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>1</v>
       </c>
@@ -1395,6 +1430,9 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,7 +1443,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1431,6 +1469,9 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1438,14 +1479,12 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>3</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1463,6 +1502,9 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1472,9 +1514,7 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>2</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
@@ -1482,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -1491,12 +1531,15 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1506,9 +1549,7 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1531,7 +1572,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1540,9 +1584,7 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
@@ -1565,6 +1607,9 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1574,14 +1619,12 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1599,6 +1642,9 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1608,9 +1654,7 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1633,7 +1677,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1642,17 +1689,34 @@
           <t>塑膠工業平上櫃</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1660,12 +1724,8 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>0</v>
       </c>
@@ -1685,6 +1745,9 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1694,9 +1757,7 @@
           <t>居家生活右下上市</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1720,6 +1781,9 @@
       </c>
       <c r="J38" t="n">
         <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1728,14 +1792,12 @@
           <t>居家生活右下上櫃</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1753,6 +1815,9 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1762,33 +1827,18 @@
           <t>居家生活平上市</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1796,14 +1846,12 @@
           <t>居家生活平上櫃</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1821,6 +1869,9 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1830,9 +1881,7 @@
           <t>建材營造右上上市</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1849,12 +1898,15 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1864,9 +1916,7 @@
           <t>建材營造右上上櫃</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
         <v>0</v>
       </c>
@@ -1889,6 +1939,9 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1898,9 +1951,7 @@
           <t>建材營造右下上市</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -1923,6 +1974,9 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1933,7 +1987,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1957,6 +2011,9 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1966,9 +2023,7 @@
           <t>建材營造平上市</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>2</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>0</v>
       </c>
@@ -1985,12 +2040,15 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2000,9 +2058,7 @@
           <t>建材營造平上櫃</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2025,6 +2081,9 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2034,9 +2093,7 @@
           <t>數位雲端右上上市</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>1</v>
       </c>
@@ -2059,6 +2116,9 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2068,9 +2128,7 @@
           <t>數位雲端右上上櫃</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2084,15 +2142,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2102,9 +2163,7 @@
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>0</v>
       </c>
@@ -2127,6 +2186,9 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2149,10 +2211,10 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -2161,6 +2223,9 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2170,9 +2235,7 @@
           <t>數位雲端平上市</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>0</v>
       </c>
@@ -2195,6 +2258,9 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2204,31 +2270,24 @@
           <t>數位雲端平上櫃</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>2</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2242,12 +2301,8 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>0</v>
       </c>
@@ -2255,6 +2310,9 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2291,6 +2349,9 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2298,9 +2359,7 @@
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>0</v>
       </c>
@@ -2323,6 +2382,9 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2332,9 +2394,7 @@
           <t>橡膠工業右上上市</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2342,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2357,6 +2417,9 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,6 +2456,9 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2400,16 +2466,16 @@
           <t>橡膠工業平上市</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
@@ -2423,6 +2489,9 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2453,6 +2522,7 @@
       <c r="J60" t="n">
         <v>0</v>
       </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2460,9 +2530,7 @@
           <t>水泥工業右下上市</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>0</v>
       </c>
@@ -2485,6 +2553,9 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2494,27 +2565,22 @@
           <t>水泥工業平上市</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2524,9 +2590,7 @@
           <t>汽車工業右上上市</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>3</v>
       </c>
@@ -2551,6 +2615,9 @@
       <c r="J63" t="n">
         <v>1</v>
       </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2585,6 +2652,9 @@
       <c r="J64" t="n">
         <v>0</v>
       </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -2592,9 +2662,7 @@
           <t>汽車工業平上市</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>0</v>
       </c>
@@ -2617,6 +2685,9 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2626,9 +2697,7 @@
           <t>油電燃氣業右上上市</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -2652,6 +2721,9 @@
       </c>
       <c r="J66" t="n">
         <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2660,9 +2732,7 @@
           <t>油電燃氣業右下上市</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -2685,6 +2755,9 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2694,9 +2767,7 @@
           <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -2719,6 +2790,9 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2728,15 +2802,11 @@
           <t>油電燃氣業平上市</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>0</v>
       </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
         <v>0</v>
       </c>
@@ -2752,19 +2822,16 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上櫃</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>0</v>
       </c>
@@ -2787,13 +2854,16 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷右下上市</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2809,39 +2879,34 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
         <v>0</v>
       </c>
@@ -2855,23 +2920,24 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業右上上市</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2883,29 +2949,30 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>2</v>
-      </c>
+          <t>生技醫療業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2914,63 +2981,67 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -2985,26 +3056,27 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -3013,44 +3085,45 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3059,20 +3132,21 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3087,24 +3161,25 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
         <v>0</v>
       </c>
@@ -3127,18 +3202,19 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>0</v>
       </c>
@@ -3161,18 +3237,19 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3195,18 +3272,19 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>0</v>
       </c>
@@ -3229,18 +3307,19 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3263,23 +3342,24 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3297,26 +3377,27 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3325,32 +3406,33 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>2</v>
-      </c>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3359,24 +3441,25 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -3393,24 +3476,25 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>0</v>
       </c>
@@ -3427,29 +3511,30 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3467,18 +3552,19 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>0</v>
       </c>
@@ -3501,18 +3587,19 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右下上市</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>0</v>
       </c>
@@ -3535,18 +3622,19 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上市</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>0</v>
       </c>
@@ -3569,18 +3657,19 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業平上市</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>0</v>
       </c>
@@ -3604,17 +3693,18 @@
       </c>
       <c r="J94" t="n">
         <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>航運業平上市</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業平上櫃</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>0</v>
       </c>
@@ -3633,22 +3723,17 @@
       <c r="H95" t="n">
         <v>0</v>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>航運業平上櫃</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右上上市</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -3658,23 +3743,34 @@
       <c r="E96" t="n">
         <v>0</v>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上市</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -3695,13 +3791,16 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上櫃</t>
+          <t>觀光事業右下上市</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3729,18 +3828,19 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -3763,18 +3863,19 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業平上市</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -3797,18 +3898,19 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上市</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業平上櫃</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>0</v>
       </c>
@@ -3824,23 +3926,26 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
+          <t>貿易百貨右上上市</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3861,18 +3966,19 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上上市</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>0</v>
       </c>
@@ -3889,24 +3995,25 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
+          <t>貿易百貨平上市</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>0</v>
       </c>
@@ -3929,18 +4036,19 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平上市</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>0</v>
       </c>
@@ -3957,24 +4065,25 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>3</v>
-      </c>
+          <t>資訊服務業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>0</v>
       </c>
@@ -3985,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3994,23 +4103,24 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>2</v>
-      </c>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -4019,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4028,23 +4138,26 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上市</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4053,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4065,18 +4178,19 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>0</v>
       </c>
@@ -4099,18 +4213,19 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平上櫃</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4133,20 +4248,21 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4169,18 +4285,17 @@
       <c r="J111" t="n">
         <v>0</v>
       </c>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -4201,40 +4316,28 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
+          <t>農業科技業平上櫃</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4244,32 +4347,33 @@
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
         <v>2</v>
       </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1</v>
-      </c>
-      <c r="I114" t="n">
-        <v>1</v>
-      </c>
       <c r="J114" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -4278,12 +4382,10 @@
           <t>通信網路業右上上櫃</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="n">
         <v>2</v>
       </c>
-      <c r="C115" t="n">
-        <v>1</v>
-      </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
@@ -4303,6 +4405,9 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4312,9 +4417,7 @@
           <t>通信網路業右下上市</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>1</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>5</v>
       </c>
@@ -4334,9 +4437,12 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4347,7 +4453,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -4356,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -4371,6 +4477,9 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4380,11 +4489,9 @@
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -4405,7 +4512,10 @@
         <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4414,17 +4524,15 @@
           <t>通信網路業平上櫃</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -4439,7 +4547,10 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -4448,9 +4559,7 @@
           <t>造紙工業右上上市</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>0</v>
       </c>
@@ -4473,6 +4582,9 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4482,9 +4594,7 @@
           <t>造紙工業右下上市</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>0</v>
       </c>
@@ -4507,6 +4617,9 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4516,9 +4629,7 @@
           <t>造紙工業平上市</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>0</v>
       </c>
@@ -4541,6 +4652,9 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4550,9 +4664,7 @@
           <t>運動休閒右上上市</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>0</v>
       </c>
@@ -4575,6 +4687,9 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4584,9 +4699,7 @@
           <t>運動休閒右上上櫃</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>0</v>
       </c>
@@ -4609,6 +4722,9 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4618,9 +4734,7 @@
           <t>運動休閒右下上市</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>0</v>
       </c>
@@ -4643,6 +4757,9 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4652,9 +4769,7 @@
           <t>運動休閒右下上櫃</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>0</v>
       </c>
@@ -4677,6 +4792,9 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4686,9 +4804,7 @@
           <t>運動休閒平上市</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -4711,6 +4827,9 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4720,9 +4839,7 @@
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>0</v>
       </c>
@@ -4745,6 +4862,9 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4754,9 +4874,7 @@
           <t>金融保險右上上市</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>1</v>
       </c>
@@ -4779,6 +4897,9 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4815,6 +4936,9 @@
       <c r="J130" t="n">
         <v>0</v>
       </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -4822,15 +4946,9 @@
           <t>金融保險平上市</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
         <v>0</v>
       </c>
@@ -4847,6 +4965,9 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4856,9 +4977,7 @@
           <t>金融業右上上櫃</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>0</v>
       </c>
@@ -4881,6 +5000,9 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4890,9 +5012,7 @@
           <t>金融業右下上櫃</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>0</v>
       </c>
@@ -4915,18 +5035,19 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>金融業平上櫃</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>0</v>
       </c>
@@ -4937,66 +5058,70 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>3</v>
-      </c>
+          <t>鋼鐵工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -5008,22 +5133,25 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
+          <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5051,18 +5179,19 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>0</v>
       </c>
@@ -5076,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -5085,18 +5214,19 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>0</v>
       </c>
@@ -5115,22 +5245,17 @@
       <c r="H139" t="n">
         <v>0</v>
       </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜右上上市</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -5144,27 +5269,28 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜右上上櫃</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>0</v>
       </c>
@@ -5181,19 +5307,22 @@
         <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5212,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -5221,18 +5350,19 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜平上市</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>0</v>
       </c>
@@ -5255,23 +5385,24 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業右上上市</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -5290,22 +5421,23 @@
       </c>
       <c r="J144" t="n">
         <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1</v>
-      </c>
+          <t>電子通路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -5320,21 +5452,22 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業右下上市</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>0</v>
       </c>
@@ -5354,16 +5487,19 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
+          <t>電子通路業右下上櫃</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5373,10 +5509,10 @@
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -5391,26 +5527,27 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業平上市</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5425,18 +5562,19 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>0</v>
       </c>
@@ -5458,126 +5596,130 @@
       <c r="I149" t="n">
         <v>0</v>
       </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="K150" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
+          <t>電子零組件業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4</v>
+      </c>
+      <c r="H151" t="n">
+        <v>6</v>
+      </c>
+      <c r="I151" t="n">
+        <v>13</v>
+      </c>
+      <c r="J151" t="n">
         <v>7</v>
       </c>
-      <c r="C151" t="n">
-        <v>5</v>
-      </c>
-      <c r="D151" t="n">
-        <v>3</v>
-      </c>
-      <c r="E151" t="n">
-        <v>4</v>
-      </c>
-      <c r="F151" t="n">
-        <v>3</v>
-      </c>
-      <c r="G151" t="n">
-        <v>5</v>
-      </c>
-      <c r="H151" t="n">
-        <v>4</v>
-      </c>
-      <c r="I151" t="n">
-        <v>9</v>
-      </c>
-      <c r="J151" t="n">
-        <v>6</v>
+      <c r="K151" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
+          <t>電子零組件業右下上市</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -5595,26 +5737,27 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平上市</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -5623,29 +5766,30 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>1</v>
-      </c>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -5654,32 +5798,33 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
         <v>2</v>
-      </c>
-      <c r="C156" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -5691,63 +5836,65 @@
         <v>2</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
+          <t>電機機械右上上櫃</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>3</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3</v>
+      </c>
+      <c r="H157" t="n">
         <v>2</v>
       </c>
-      <c r="C157" t="n">
-        <v>1</v>
-      </c>
-      <c r="D157" t="n">
-        <v>2</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" t="n">
-        <v>2</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0</v>
-      </c>
       <c r="I157" t="n">
         <v>1</v>
       </c>
       <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械右下上市</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -5756,29 +5903,32 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -5799,18 +5949,19 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>1</v>
-      </c>
+          <t>電機機械平上市</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>0</v>
       </c>
@@ -5833,23 +5984,24 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械平上櫃</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -5867,18 +6019,19 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>1</v>
       </c>
@@ -5886,81 +6039,83 @@
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="n">
         <v>2</v>
       </c>
-      <c r="C163" t="n">
-        <v>1</v>
-      </c>
       <c r="D163" t="n">
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>2</v>
-      </c>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5969,20 +6124,23 @@
         <v>1</v>
       </c>
       <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -5991,32 +6149,33 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -6025,35 +6184,36 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>1</v>
-      </c>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -6068,21 +6228,22 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>1</v>
-      </c>
+          <t>食品工業右上上市</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -6105,18 +6266,19 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
         <v>0</v>
       </c>
@@ -6139,18 +6301,19 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
         <v>0</v>
       </c>
@@ -6158,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6173,13 +6336,16 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
+          <t>食品工業右下上櫃</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6207,60 +6373,42 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
         <v>0</v>
       </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" t="n">
-        <v>0</v>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -6268,49 +6416,10 @@
       <c r="G173" t="n">
         <v>0</v>
       </c>
-      <c r="H173" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" t="n">
-        <v>0</v>
-      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -491,33 +486,32 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10</v>
-      </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -526,33 +520,32 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +554,9 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
@@ -569,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -584,10 +579,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -621,10 +613,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -633,21 +622,23 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -656,9 +647,6 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -668,9 +656,11 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -679,22 +669,19 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +690,32 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -738,32 +724,31 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -773,9 +758,11 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -796,9 +783,6 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -809,33 +793,30 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -845,7 +826,9 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -859,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -868,9 +851,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -880,7 +860,9 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
@@ -888,24 +870,21 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -915,33 +894,32 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>5</v>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -950,34 +928,33 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -985,7 +962,9 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
@@ -1008,9 +987,6 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1024,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1045,9 +1021,6 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1057,21 +1030,23 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1080,9 +1055,6 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1092,18 +1064,20 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1112,13 +1086,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1127,33 +1098,32 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1162,7 +1132,9 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1176,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -1185,10 +1157,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1197,7 +1166,9 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1220,9 +1191,6 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1232,7 +1200,9 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
@@ -1240,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1255,9 +1225,6 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1267,7 +1234,9 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1278,22 +1247,19 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1302,7 +1268,9 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
@@ -1310,24 +1278,21 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,33 +1302,32 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
         <v>6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1372,33 +1336,32 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
         <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1407,32 +1370,31 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -1464,12 +1426,9 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1479,18 +1438,20 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1502,9 +1463,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1514,9 +1472,11 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -1525,21 +1485,18 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1549,7 +1506,9 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1569,13 +1528,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1584,7 +1540,9 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
@@ -1607,9 +1565,6 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1619,7 +1574,9 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1642,9 +1599,6 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1654,7 +1608,9 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1671,30 +1627,29 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>居家生活右上上櫃</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1712,20 +1667,21 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>居家生活右下上市</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
@@ -1739,25 +1695,24 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>居家生活右下上櫃</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1771,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1780,24 +1735,23 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>居家生活平上市</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1812,41 +1766,55 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+          <t>居家生活平上櫃</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>建材營造右上上市</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -1869,19 +1837,18 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>建材營造右上上櫃</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1898,25 +1865,24 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
@@ -1939,19 +1905,18 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>建材營造右下上櫃</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -1974,23 +1939,20 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
+          <t>建材營造平上市</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1999,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2011,19 +1973,18 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>建材營造平上櫃</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
@@ -2046,19 +2007,18 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>數位雲端右上上市</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2081,30 +2041,29 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>數位雲端右上上櫃</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2116,19 +2075,18 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2136,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2145,27 +2103,26 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>數位雲端右下上櫃</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2174,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2186,16 +2143,13 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2208,42 +2162,41 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>數位雲端平上櫃</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2258,72 +2211,81 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2338,33 +2300,28 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>橡膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2382,19 +2339,18 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>橡膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2417,24 +2373,19 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
+          <t>橡膠工業平上市</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
         <v>0</v>
       </c>
@@ -2454,16 +2405,13 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
+          <t>水泥工業右上上市</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2491,19 +2439,22 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>水泥工業右下上市</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
@@ -2522,27 +2473,24 @@
       <c r="J60" t="n">
         <v>0</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
+          <t>水泥工業平上市</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>0</v>
       </c>
@@ -2553,58 +2501,66 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>汽車工業右上上市</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>汽車工業右下上市</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2614,15 +2570,12 @@
       </c>
       <c r="J63" t="n">
         <v>1</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2650,19 +2603,18 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>油電燃氣業右上上市</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
@@ -2670,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2679,25 +2631,24 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上上市</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>油電燃氣業右下上市</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -2711,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2720,19 +2671,18 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
-      </c>
-      <c r="K66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>油電燃氣業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -2755,19 +2705,18 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>油電燃氣業平上市</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -2790,23 +2739,24 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>油電燃氣業平上櫃</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
@@ -2822,8 +2772,9 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -2831,18 +2782,20 @@
           <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2854,9 +2807,6 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2893,9 +2843,6 @@
       <c r="J71" t="n">
         <v>0</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -2903,10 +2850,18 @@
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
@@ -2920,9 +2875,6 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2932,32 +2884,31 @@
           <t>生技醫療業右上上市</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2967,18 +2918,20 @@
           <t>生技醫療業右上上櫃</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
         <v>3</v>
@@ -2987,13 +2940,10 @@
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -3009,28 +2959,25 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3039,32 +2986,31 @@
           <t>生技醫療業右下上櫃</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3074,32 +3020,31 @@
           <t>生技醫療業平上市</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3109,9 +3054,11 @@
           <t>生技醫療業平上櫃</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3120,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3132,9 +3079,6 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3144,7 +3088,9 @@
           <t>紡織纖維右上上市</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
@@ -3161,16 +3107,13 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3179,7 +3122,9 @@
           <t>紡織纖維右上上櫃</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
@@ -3202,9 +3147,6 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3214,7 +3156,9 @@
           <t>紡織纖維右下上市</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
@@ -3237,9 +3181,6 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3249,7 +3190,9 @@
           <t>紡織纖維右下上櫃</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3272,9 +3215,6 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3284,7 +3224,9 @@
           <t>紡織纖維平上市</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
@@ -3307,9 +3249,6 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3319,7 +3258,9 @@
           <t>紡織纖維平上櫃</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3342,9 +3283,6 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3354,12 +3292,14 @@
           <t>綠能環保右上上市</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3377,9 +3317,6 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3389,33 +3326,32 @@
           <t>綠能環保右上上櫃</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -3424,7 +3360,9 @@
           <t>綠能環保右下上市</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
@@ -3441,15 +3379,12 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3459,7 +3394,9 @@
           <t>綠能環保右下上櫃</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -3470,22 +3407,19 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3494,7 +3428,9 @@
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
@@ -3517,9 +3453,6 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3529,7 +3462,9 @@
           <t>綠能環保平上櫃</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
@@ -3549,12 +3484,9 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3564,7 +3496,9 @@
           <t>航運業右上上市</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
@@ -3584,12 +3518,9 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3599,7 +3530,9 @@
           <t>航運業右下上市</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
@@ -3622,9 +3555,6 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3634,7 +3564,9 @@
           <t>航運業右下上櫃</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
@@ -3657,9 +3589,6 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3669,7 +3598,9 @@
           <t>航運業平上市</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
@@ -3693,9 +3624,6 @@
       </c>
       <c r="J94" t="n">
         <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3704,28 +3632,19 @@
           <t>航運業平上櫃</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3733,7 +3652,9 @@
           <t>觀光事業右上上市</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -3756,9 +3677,6 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3768,9 +3686,11 @@
           <t>觀光事業右上上櫃</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -3791,9 +3711,6 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3830,9 +3747,6 @@
       <c r="J98" t="n">
         <v>0</v>
       </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -3840,7 +3754,9 @@
           <t>觀光事業右下上櫃</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -3863,10 +3779,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -3875,7 +3788,9 @@
           <t>觀光事業平上市</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -3885,22 +3800,15 @@
       <c r="E100" t="n">
         <v>0</v>
       </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>0</v>
       </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3910,7 +3818,9 @@
           <t>觀光事業平上櫃</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
@@ -3929,11 +3839,10 @@
       <c r="H101" t="n">
         <v>0</v>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
       <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3943,7 +3852,9 @@
           <t>貿易百貨右上上市</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
@@ -3966,9 +3877,6 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3978,7 +3886,9 @@
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
@@ -3995,15 +3905,12 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4013,7 +3920,9 @@
           <t>貿易百貨平上市</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
@@ -4024,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4036,9 +3945,6 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4048,7 +3954,9 @@
           <t>資訊服務業右上上市</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
@@ -4071,9 +3979,6 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4083,33 +3988,32 @@
           <t>資訊服務業右上上櫃</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4118,7 +4022,9 @@
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
@@ -4141,9 +4047,6 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4157,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4166,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4178,9 +4081,6 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4190,7 +4090,9 @@
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
@@ -4213,9 +4115,6 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4225,7 +4124,9 @@
           <t>資訊服務業平上櫃</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4249,9 +4150,6 @@
       </c>
       <c r="J110" t="n">
         <v>1</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4260,9 +4158,11 @@
           <t>農業科技業右上上櫃</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4285,7 +4185,6 @@
       <c r="J111" t="n">
         <v>0</v>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4293,7 +4192,9 @@
           <t>農業科技業右下上櫃</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
@@ -4316,87 +4217,100 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平上櫃</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="n">
-        <v>0</v>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>通信網路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
       <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
         <v>3</v>
       </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1</v>
-      </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>5</v>
-      </c>
-      <c r="K114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>通信網路業右下上市</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4405,21 +4319,20 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>4</v>
-      </c>
-      <c r="K115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上市</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -4431,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -4440,58 +4353,54 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上市</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上市</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>通信網路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -4506,25 +4415,24 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>造紙工業右上上市</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
@@ -4547,19 +4455,18 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右上上市</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>造紙工業右下上市</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
@@ -4582,19 +4489,18 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下上市</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>造紙工業平上市</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
@@ -4617,19 +4523,18 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平上市</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>運動休閒右上上市</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
@@ -4652,21 +4557,20 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上市</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>運動休閒右上上櫃</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -4687,27 +4591,26 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上櫃</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -4722,19 +4625,18 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>運動休閒右下上櫃</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
@@ -4757,19 +4659,18 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上櫃</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>運動休閒平上市</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
@@ -4792,19 +4693,18 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上市</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -4827,19 +4727,18 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>金融保險右上上市</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
@@ -4862,21 +4761,20 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上上市</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>金融保險右下上市</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -4897,16 +4795,13 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下上市</t>
+          <t>金融保險平上市</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -4934,26 +4829,29 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
+          <t>金融業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4965,19 +4863,18 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>金融業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>金融業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
@@ -4994,25 +4891,24 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>金融業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>金融業平上櫃</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
@@ -5035,9 +4931,6 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5047,32 +4940,31 @@
           <t>鋼鐵工業右上上市</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5082,33 +4974,32 @@
           <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I135" t="n">
         <v>2</v>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
-      </c>
-      <c r="K135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5144,9 +5035,6 @@
       <c r="J136" t="n">
         <v>0</v>
       </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -5179,9 +5067,6 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
-      </c>
-      <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5191,7 +5076,9 @@
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
@@ -5205,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -5214,9 +5101,6 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5226,7 +5110,9 @@
           <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
@@ -5243,11 +5129,14 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -5255,7 +5144,9 @@
           <t>電器電纜右上上市</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -5263,24 +5154,21 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5290,7 +5178,9 @@
           <t>電器電纜右上上櫃</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
@@ -5298,13 +5188,13 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -5313,9 +5203,6 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5352,9 +5239,6 @@
       <c r="J142" t="n">
         <v>0</v>
       </c>
-      <c r="K142" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -5362,7 +5246,9 @@
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
@@ -5385,9 +5271,6 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5397,12 +5280,14 @@
           <t>電子通路業右上上市</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -5417,13 +5302,10 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -5432,7 +5314,9 @@
           <t>電子通路業右上上櫃</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
@@ -5446,18 +5330,15 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5467,7 +5348,9 @@
           <t>電子通路業右下上市</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
@@ -5490,9 +5373,6 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5503,16 +5383,16 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -5527,9 +5407,6 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5539,7 +5416,9 @@
           <t>電子通路業平上市</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -5562,9 +5441,6 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5574,7 +5450,9 @@
           <t>電子通路業平上櫃</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
@@ -5596,8 +5474,9 @@
       <c r="I149" t="n">
         <v>0</v>
       </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -5605,7 +5484,9 @@
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>3</v>
+      </c>
       <c r="C150" t="n">
         <v>4</v>
       </c>
@@ -5619,19 +5500,16 @@
         <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I150" t="n">
         <v>10</v>
       </c>
       <c r="J150" t="n">
-        <v>6</v>
-      </c>
-      <c r="K150" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -5640,33 +5518,32 @@
           <t>電子零組件業右上上櫃</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
       <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>5</v>
+      </c>
+      <c r="E151" t="n">
         <v>3</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
       </c>
       <c r="F151" t="n">
         <v>5</v>
       </c>
       <c r="G151" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I151" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J151" t="n">
-        <v>7</v>
-      </c>
-      <c r="K151" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -5676,7 +5553,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -5688,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -5700,9 +5577,6 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5725,21 +5599,18 @@
         <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
-      </c>
-      <c r="K153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5749,32 +5620,31 @@
           <t>電子零組件業平上市</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
         <v>2</v>
       </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="n">
-        <v>2</v>
-      </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
       <c r="J154" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5784,32 +5654,31 @@
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
-      </c>
-      <c r="K155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5819,21 +5688,23 @@
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
         <v>2</v>
       </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -5843,9 +5714,6 @@
       </c>
       <c r="J156" t="n">
         <v>0</v>
-      </c>
-      <c r="K156" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -5854,32 +5722,31 @@
           <t>電機機械右上上櫃</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
       <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
         <v>3</v>
       </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5889,9 +5756,11 @@
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -5912,9 +5781,6 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5951,9 +5817,6 @@
       <c r="J159" t="n">
         <v>0</v>
       </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -5961,7 +5824,9 @@
           <t>電機機械平上市</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
@@ -5984,9 +5849,6 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5996,12 +5858,14 @@
           <t>電機機械平上櫃</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -6019,9 +5883,6 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6031,33 +5892,32 @@
           <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
       <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
-      </c>
-      <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -6066,32 +5926,31 @@
           <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6101,7 +5960,9 @@
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
       <c r="C164" t="n">
         <v>0</v>
       </c>
@@ -6112,22 +5973,19 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -6140,16 +5998,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -6161,9 +6019,6 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6173,7 +6028,9 @@
           <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
@@ -6187,18 +6044,15 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6208,12 +6062,14 @@
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -6231,9 +6087,6 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6243,7 +6096,9 @@
           <t>食品工業右上上市</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -6266,9 +6121,6 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6278,7 +6130,9 @@
           <t>食品工業右上上櫃</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
@@ -6301,9 +6155,6 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6313,7 +6164,9 @@
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
@@ -6321,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -6336,9 +6189,6 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6375,9 +6225,6 @@
       <c r="J171" t="n">
         <v>0</v>
       </c>
-      <c r="K171" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -6385,18 +6232,33 @@
           <t>食品工業平上市</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -6404,9 +6266,15 @@
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
@@ -6416,10 +6284,15 @@
       <c r="G173" t="n">
         <v>0</v>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J173"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -486,9 +491,7 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -496,7 +499,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -513,6 +516,9 @@
       <c r="J2" t="n">
         <v>4</v>
       </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -520,11 +526,9 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -533,7 +537,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
@@ -545,7 +549,10 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -554,9 +561,7 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
@@ -564,7 +569,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -579,7 +584,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +621,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -622,9 +633,7 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -647,7 +656,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -656,11 +668,9 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -669,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -681,7 +691,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -690,9 +703,7 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
@@ -700,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -716,6 +727,9 @@
       </c>
       <c r="J8" t="n">
         <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -724,9 +738,7 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>1</v>
       </c>
@@ -751,6 +763,9 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -758,9 +773,7 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
@@ -783,6 +796,9 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -802,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -817,7 +833,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -826,9 +845,7 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -836,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -852,6 +869,9 @@
       </c>
       <c r="J12" t="n">
         <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -860,9 +880,7 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
@@ -870,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -885,7 +903,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -894,9 +915,7 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>1</v>
       </c>
@@ -921,6 +940,9 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -928,32 +950,33 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -962,9 +985,7 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
@@ -987,6 +1008,9 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1000,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1022,6 +1046,9 @@
       </c>
       <c r="J17" t="n">
         <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1030,9 +1057,7 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -1055,6 +1080,9 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1064,20 +1092,18 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1086,10 +1112,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1098,9 +1127,7 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>1</v>
       </c>
@@ -1111,19 +1138,22 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1132,9 +1162,7 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1142,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1159,6 +1187,9 @@
       <c r="J21" t="n">
         <v>4</v>
       </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1166,9 +1197,7 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1191,6 +1220,9 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1200,9 +1232,7 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
@@ -1210,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1225,6 +1255,9 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1234,9 +1267,7 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1247,19 +1278,22 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1268,9 +1302,7 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
@@ -1281,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1293,6 +1325,9 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,9 +1337,7 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>4</v>
       </c>
@@ -1329,6 +1362,9 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1336,33 +1372,34 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>7</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
         <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1370,9 +1407,7 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
@@ -1395,6 +1430,9 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1404,9 +1442,7 @@
           <t>半導體業右下上櫃</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>2</v>
       </c>
@@ -1431,6 +1467,9 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1438,9 +1477,7 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1463,6 +1500,9 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1472,32 +1512,33 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1506,9 +1547,7 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1525,13 +1564,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1540,9 +1582,7 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
@@ -1565,6 +1605,9 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1574,9 +1617,7 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1599,6 +1640,9 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1608,9 +1652,7 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1627,24 +1669,25 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
+          <t>塑膠工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
@@ -1669,16 +1712,15 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+          <t>居家生活右上上櫃</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1695,24 +1737,25 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+          <t>居家生活右下上市</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1726,27 +1769,28 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
+          <t>居家生活右下上櫃</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1760,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1769,6 +1813,9 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,9 +1825,7 @@
           <t>居家生活平上櫃</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
@@ -1803,6 +1848,9 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1812,9 +1860,7 @@
           <t>建材營造右上上市</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -1825,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1837,6 +1883,9 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1846,9 +1895,7 @@
           <t>建材營造右上上櫃</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1871,6 +1918,9 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1907,6 +1957,9 @@
       <c r="J43" t="n">
         <v>0</v>
       </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1914,9 +1967,7 @@
           <t>建材營造右下上櫃</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -1939,6 +1990,9 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1948,9 +2002,7 @@
           <t>建材營造平上市</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>0</v>
       </c>
@@ -1961,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1973,6 +2025,9 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1982,9 +2037,7 @@
           <t>建材營造平上櫃</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
         <v>0</v>
       </c>
@@ -2007,6 +2060,9 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2016,9 +2072,7 @@
           <t>數位雲端右上上市</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2041,6 +2095,9 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2050,9 +2107,7 @@
           <t>數位雲端右上上櫃</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>1</v>
       </c>
@@ -2060,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2076,6 +2131,9 @@
       </c>
       <c r="J48" t="n">
         <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2084,9 +2142,7 @@
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2109,6 +2165,9 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2118,17 +2177,15 @@
           <t>數位雲端右下上櫃</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -2143,6 +2200,9 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2152,9 +2212,7 @@
           <t>數位雲端平上市</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2177,6 +2235,9 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2186,20 +2247,16 @@
           <t>數位雲端平上櫃</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2211,6 +2268,9 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2222,12 +2282,8 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>0</v>
       </c>
@@ -2241,6 +2297,9 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2277,6 +2336,9 @@
       <c r="J54" t="n">
         <v>0</v>
       </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -2284,9 +2346,7 @@
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2305,8 +2365,15 @@
       <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2314,9 +2381,7 @@
           <t>橡膠工業右上上市</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>1</v>
       </c>
@@ -2339,6 +2404,9 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2348,9 +2416,7 @@
           <t>橡膠工業右下上市</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2373,6 +2439,9 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2382,10 +2451,10 @@
           <t>橡膠工業平上市</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
@@ -2405,6 +2474,9 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2433,10 +2505,11 @@
       <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,9 +2519,7 @@
           <t>水泥工業右下上市</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>0</v>
       </c>
@@ -2471,6 +2542,9 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2480,27 +2554,20 @@
           <t>水泥工業平上市</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2510,9 +2577,7 @@
           <t>汽車工業右上上市</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>1</v>
       </c>
@@ -2537,6 +2602,9 @@
       <c r="J62" t="n">
         <v>1</v>
       </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2544,9 +2612,7 @@
           <t>汽車工業右下上市</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>0</v>
       </c>
@@ -2570,6 +2636,9 @@
       </c>
       <c r="J63" t="n">
         <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2578,9 +2647,7 @@
           <t>汽車工業平上市</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -2603,6 +2670,9 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2612,9 +2682,7 @@
           <t>油電燃氣業右上上市</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>0</v>
       </c>
@@ -2637,6 +2705,9 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2646,9 +2717,7 @@
           <t>油電燃氣業右下上市</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -2671,6 +2740,9 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2680,9 +2752,7 @@
           <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -2705,6 +2775,9 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2714,9 +2787,7 @@
           <t>油電燃氣業平上市</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -2732,36 +2803,31 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
         <v>0</v>
       </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上櫃</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2774,28 +2840,29 @@
       </c>
       <c r="J69" t="n">
         <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷右下上市</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2807,21 +2874,20 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
         <v>0</v>
       </c>
@@ -2841,18 +2907,19 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業右上上市</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>0</v>
       </c>
@@ -2863,10 +2930,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2875,18 +2942,19 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
+          <t>生技醫療業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>0</v>
       </c>
@@ -2894,67 +2962,71 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
         <v>2</v>
       </c>
-      <c r="G74" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2</v>
-      </c>
-      <c r="I74" t="n">
-        <v>1</v>
-      </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>0</v>
       </c>
@@ -2965,72 +3037,74 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3039,24 +3113,25 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>0</v>
       </c>
@@ -3067,30 +3142,31 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>0</v>
       </c>
@@ -3107,24 +3183,25 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
         <v>0</v>
       </c>
@@ -3147,18 +3224,19 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>0</v>
       </c>
@@ -3181,18 +3259,19 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3215,18 +3294,19 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>0</v>
       </c>
@@ -3249,18 +3329,19 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3284,19 +3365,20 @@
       </c>
       <c r="J84" t="n">
         <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3305,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3314,23 +3396,24 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3339,30 +3422,31 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>0</v>
       </c>
@@ -3373,30 +3457,31 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -3407,30 +3492,31 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>0</v>
       </c>
@@ -3453,18 +3539,19 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>0</v>
       </c>
@@ -3484,21 +3571,22 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右下上市</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>0</v>
       </c>
@@ -3518,21 +3606,22 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上市</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>0</v>
       </c>
@@ -3555,18 +3644,19 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業平上市</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>0</v>
       </c>
@@ -3586,21 +3676,22 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>航運業平上市</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業平上櫃</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>0</v>
       </c>
@@ -3613,48 +3704,58 @@
       <c r="F94" t="n">
         <v>0</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>航運業平上櫃</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右上上市</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>0</v>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上市</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -3677,18 +3778,19 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右下上市</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>0</v>
       </c>
@@ -3711,18 +3813,19 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>0</v>
       </c>
@@ -3745,18 +3848,19 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業平上市</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -3779,18 +3883,19 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上市</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業平上櫃</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -3800,27 +3905,30 @@
       <c r="E100" t="n">
         <v>0</v>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
+          <t>貿易百貨右上上市</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>0</v>
       </c>
@@ -3843,18 +3951,19 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上上市</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
         <v>0</v>
       </c>
@@ -3865,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3877,18 +3986,19 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
+          <t>貿易百貨平上市</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>0</v>
       </c>
@@ -3911,18 +4021,19 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平上市</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>0</v>
       </c>
@@ -3933,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3945,23 +4056,24 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3970,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3979,23 +4091,24 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -4004,32 +4117,33 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -4047,18 +4161,19 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>0</v>
       </c>
@@ -4081,18 +4196,19 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平上櫃</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>0</v>
       </c>
@@ -4109,24 +4225,25 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4145,22 +4262,19 @@
       <c r="H110" t="n">
         <v>0</v>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>1</v>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>0</v>
       </c>
@@ -4184,41 +4298,31 @@
       </c>
       <c r="J111" t="n">
         <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
+          <t>農業科技業平上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -4226,9 +4330,7 @@
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>1</v>
       </c>
@@ -4242,15 +4344,18 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4260,9 +4365,7 @@
           <t>通信網路業右上上櫃</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>0</v>
       </c>
@@ -4279,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I114" t="n">
         <v>3</v>
@@ -4287,6 +4390,9 @@
       <c r="J114" t="n">
         <v>0</v>
       </c>
+      <c r="K114" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -4294,9 +4400,7 @@
           <t>通信網路業右下上市</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>0</v>
       </c>
@@ -4310,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4320,6 +4424,9 @@
       </c>
       <c r="J115" t="n">
         <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -4328,11 +4435,9 @@
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -4354,6 +4459,9 @@
       </c>
       <c r="J116" t="n">
         <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4362,9 +4470,7 @@
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>0</v>
       </c>
@@ -4381,13 +4487,16 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4396,11 +4505,9 @@
           <t>通信網路業平上櫃</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -4415,13 +4522,16 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -4430,9 +4540,7 @@
           <t>造紙工業右上上市</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>0</v>
       </c>
@@ -4455,6 +4563,9 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4464,9 +4575,7 @@
           <t>造紙工業右下上市</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>0</v>
       </c>
@@ -4489,6 +4598,9 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4498,9 +4610,7 @@
           <t>造紙工業平上市</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>0</v>
       </c>
@@ -4523,6 +4633,9 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4532,9 +4645,7 @@
           <t>運動休閒右上上市</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>0</v>
       </c>
@@ -4557,6 +4668,9 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4566,9 +4680,7 @@
           <t>運動休閒右上上櫃</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
         <v>1</v>
       </c>
@@ -4591,6 +4703,9 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4600,9 +4715,7 @@
           <t>運動休閒右下上市</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>0</v>
       </c>
@@ -4625,6 +4738,9 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4634,9 +4750,7 @@
           <t>運動休閒右下上櫃</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>0</v>
       </c>
@@ -4659,6 +4773,9 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4668,9 +4785,7 @@
           <t>運動休閒平上市</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
         <v>0</v>
       </c>
@@ -4693,6 +4808,9 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4702,9 +4820,7 @@
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -4727,6 +4843,9 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4736,9 +4855,7 @@
           <t>金融保險右上上市</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>0</v>
       </c>
@@ -4761,6 +4878,9 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4770,9 +4890,7 @@
           <t>金融保險右下上市</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>0</v>
       </c>
@@ -4795,6 +4913,9 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4804,9 +4925,7 @@
           <t>金融保險平上市</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
         <v>0</v>
       </c>
@@ -4829,6 +4948,9 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4838,9 +4960,7 @@
           <t>金融業右上上櫃</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
         <v>0</v>
       </c>
@@ -4864,6 +4984,9 @@
       </c>
       <c r="J131" t="n">
         <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4872,9 +4995,7 @@
           <t>金融業右下上櫃</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>0</v>
       </c>
@@ -4897,86 +5018,89 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>金融業平上櫃</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1</v>
-      </c>
+          <t>鋼鐵工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>0</v>
       </c>
@@ -4984,33 +5108,34 @@
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>0</v>
       </c>
@@ -5027,24 +5152,25 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>0</v>
       </c>
@@ -5052,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -5067,18 +5193,19 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>0</v>
       </c>
@@ -5091,28 +5218,23 @@
       <c r="F138" t="n">
         <v>0</v>
       </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜右上上市</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>0</v>
       </c>
@@ -5120,33 +5242,34 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜右上上櫃</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -5157,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5169,18 +5292,19 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜右下上市</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>0</v>
       </c>
@@ -5188,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -5203,18 +5327,19 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
+          <t>電器電纜平上市</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>0</v>
       </c>
@@ -5237,18 +5362,19 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業右上上市</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
         <v>0</v>
       </c>
@@ -5268,21 +5394,22 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1</v>
-      </c>
+          <t>電子通路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>0</v>
       </c>
@@ -5296,27 +5423,28 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業右下上市</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>0</v>
       </c>
@@ -5330,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -5339,20 +5467,21 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -5373,20 +5502,21 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1</v>
-      </c>
+          <t>電子通路業平上市</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -5407,18 +5537,19 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -5434,127 +5565,127 @@
       <c r="G148" t="n">
         <v>0</v>
       </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K149" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>3</v>
-      </c>
+          <t>電子零組件業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E150" t="n">
         <v>4</v>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G150" t="n">
+        <v>13</v>
+      </c>
+      <c r="H150" t="n">
+        <v>7</v>
+      </c>
+      <c r="I150" t="n">
         <v>9</v>
-      </c>
-      <c r="H150" t="n">
-        <v>6</v>
-      </c>
-      <c r="I150" t="n">
-        <v>10</v>
       </c>
       <c r="J150" t="n">
         <v>2</v>
       </c>
+      <c r="K150" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1</v>
-      </c>
+          <t>電子零組件業右下上市</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1</v>
-      </c>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>1</v>
       </c>
@@ -5571,26 +5702,27 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平上市</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -5599,10 +5731,10 @@
         <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -5611,18 +5743,19 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1</v>
-      </c>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
         <v>0</v>
       </c>
@@ -5633,30 +5766,31 @@
         <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
         <v>0</v>
       </c>
@@ -5667,42 +5801,43 @@
         <v>2</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
+          <t>電機機械右上上櫃</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" t="n">
         <v>2</v>
       </c>
-      <c r="C156" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
       <c r="G156" t="n">
         <v>1</v>
       </c>
@@ -5710,21 +5845,22 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>1</v>
-      </c>
+          <t>電機機械右下上市</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>0</v>
       </c>
@@ -5732,13 +5868,13 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -5747,13 +5883,16 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5781,18 +5920,19 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械平上市</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>0</v>
       </c>
@@ -5815,18 +5955,19 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械平上櫃</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>0</v>
       </c>
@@ -5849,94 +5990,99 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -5951,32 +6097,33 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5985,29 +6132,30 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -6019,18 +6167,19 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
         <v>0</v>
       </c>
@@ -6044,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -6053,18 +6202,19 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右上上市</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>0</v>
       </c>
@@ -6087,18 +6237,19 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -6121,20 +6272,21 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -6155,18 +6307,19 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
         <v>0</v>
       </c>
@@ -6189,54 +6342,42 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
         <v>0</v>
       </c>
-      <c r="D171" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0</v>
-      </c>
-      <c r="H171" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" t="n">
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -6244,53 +6385,14 @@
       <c r="E172" t="n">
         <v>0</v>
       </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0</v>
-      </c>
-      <c r="H173" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" t="n">
+      <c r="K172" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K172"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -491,34 +486,33 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
       <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -526,32 +520,31 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -561,9 +554,11 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -578,15 +573,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -615,15 +607,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -633,15 +622,17 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -656,10 +647,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -668,32 +656,31 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -703,33 +690,32 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -738,33 +724,32 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +758,9 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
@@ -796,9 +783,6 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -809,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -845,7 +826,9 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -853,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -869,9 +852,6 @@
       </c>
       <c r="J12" t="n">
         <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -880,9 +860,11 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -894,18 +876,15 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -915,33 +894,32 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -950,33 +928,32 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +962,9 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
@@ -1008,9 +987,6 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,9 +1021,6 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1057,15 +1030,17 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1080,9 +1055,6 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1092,12 +1064,14 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1106,18 +1080,15 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1127,33 +1098,32 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1162,7 +1132,9 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1179,16 +1151,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1197,7 +1166,9 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1220,9 +1191,6 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1232,9 +1200,11 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1255,9 +1225,6 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1267,32 +1234,31 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,32 +1268,31 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,33 +1302,32 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
       <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
         <v>4</v>
       </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1372,33 +1336,32 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
         <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1407,18 +1370,20 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1430,9 +1395,6 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1442,12 +1404,14 @@
           <t>半導體業右下上櫃</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1456,19 +1420,16 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1477,12 +1438,14 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1500,9 +1463,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1512,7 +1472,9 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
@@ -1520,25 +1482,22 @@
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1547,7 +1506,9 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1561,18 +1522,15 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1582,7 +1540,9 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1565,6 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1617,7 +1574,9 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1640,9 +1599,6 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1652,7 +1608,9 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1663,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1675,44 +1633,26 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業平上櫃</t>
+          <t>居家生活右上上市</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1720,7 +1660,9 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1743,9 +1685,6 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1755,7 +1694,9 @@
           <t>居家生活右下上市</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
@@ -1766,21 +1707,18 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1790,7 +1728,9 @@
           <t>居家生活右下上櫃</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
@@ -1798,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1813,19 +1753,18 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>居家生活平上市</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
@@ -1848,19 +1787,18 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>居家生活平上櫃</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -1871,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1883,19 +1821,18 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>建材營造右上上市</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
@@ -1918,16 +1855,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
+          <t>建材營造右上上櫃</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1955,19 +1889,18 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -1990,19 +1923,18 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>建材營造右下上櫃</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
@@ -2025,24 +1957,23 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>建材營造平上市</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2060,19 +1991,18 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>建材營造平上櫃</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2095,21 +2025,20 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>數位雲端右上上市</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2118,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2131,23 +2060,22 @@
       </c>
       <c r="J48" t="n">
         <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>數位雲端右上上櫃</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2162,33 +2090,32 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2200,24 +2127,23 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>數位雲端右下上櫃</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2235,28 +2161,29 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2268,22 +2195,27 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>數位雲端平上櫃</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
@@ -2297,16 +2229,13 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2319,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2328,27 +2257,26 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2357,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2366,24 +2294,23 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2394,29 +2321,24 @@
       <c r="F56" t="n">
         <v>0</v>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>橡膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2439,19 +2361,18 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>橡膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2474,19 +2395,18 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>橡膠工業平上市</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
@@ -2505,21 +2425,22 @@
       <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
       <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>水泥工業右上上市</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
@@ -2542,50 +2463,58 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>水泥工業右下上市</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="n">
+      <c r="J61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>水泥工業平上市</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2594,27 +2523,22 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>汽車工業右上上市</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2623,31 +2547,30 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>汽車工業右下上市</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -2664,25 +2587,24 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上上市</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>汽車工業平上市</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
@@ -2690,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2699,27 +2621,26 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>油電燃氣業右上上市</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -2728,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2740,19 +2661,18 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>油電燃氣業右下上市</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -2775,19 +2695,18 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>油電燃氣業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -2803,31 +2722,36 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>油電燃氣業平上市</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2840,18 +2764,17 @@
       </c>
       <c r="J69" t="n">
         <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>油電燃氣業平上櫃</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
@@ -2870,26 +2793,23 @@
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -2904,22 +2824,21 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>玻璃陶瓷右下上市</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
@@ -2930,10 +2849,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2942,19 +2861,18 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
@@ -2962,44 +2880,37 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
+          <t>生技醫療業右上上市</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3008,60 +2919,58 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>生技醫療業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>生技醫療業右下上市</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
@@ -3069,13 +2978,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -3084,19 +2993,18 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
@@ -3104,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3119,21 +3027,20 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3142,36 +3049,35 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3189,19 +3095,18 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
@@ -3212,31 +3117,30 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
@@ -3259,19 +3163,18 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3294,19 +3197,18 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
@@ -3329,19 +3231,18 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3365,20 +3266,19 @@
       </c>
       <c r="J84" t="n">
         <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3387,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3396,22 +3296,21 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
@@ -3428,60 +3327,58 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -3492,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3501,33 +3398,32 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3539,19 +3435,18 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
@@ -3574,19 +3469,18 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上市</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
@@ -3600,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3609,19 +3503,18 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
@@ -3635,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3644,19 +3537,18 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>航運業平上市</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>航運業右下上市</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
@@ -3676,22 +3568,21 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>航運業平上櫃</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>航運業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
@@ -3704,23 +3595,28 @@
       <c r="F94" t="n">
         <v>0</v>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
       <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上市</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>航運業平上市</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
@@ -3743,54 +3639,38 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上櫃</t>
+          <t>航運業平上櫃</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>觀光事業右上上市</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
@@ -3813,19 +3693,18 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>觀光事業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
@@ -3848,19 +3727,18 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
-      </c>
-      <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上市</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>觀光事業右下上市</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -3883,19 +3761,18 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>觀光事業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -3908,39 +3785,36 @@
       <c r="F100" t="n">
         <v>0</v>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上上市</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>觀光事業平上市</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
         <v>0</v>
       </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>0</v>
       </c>
@@ -3950,20 +3824,17 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>觀光事業平上櫃</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
@@ -3974,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3986,19 +3857,18 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平上市</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>貿易百貨右上上市</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
@@ -4021,19 +3891,18 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
@@ -4056,19 +3925,18 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>貿易百貨平上市</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
@@ -4082,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4091,19 +3959,18 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
@@ -4126,54 +3993,52 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>資訊服務業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
-      </c>
-      <c r="K107" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
@@ -4196,19 +4061,18 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>資訊服務業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
@@ -4225,25 +4089,24 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4262,19 +4125,22 @@
       <c r="H110" t="n">
         <v>0</v>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>資訊服務業平上櫃</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
@@ -4291,153 +4157,146 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
-      </c>
-      <c r="K113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上櫃</t>
+          <t>農業科技業平上櫃</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>4</v>
-      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>3</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上市</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>通信網路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -4446,66 +4305,64 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>1</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上市</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>通信網路業右下上市</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
@@ -4522,25 +4379,24 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右上上市</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>通信網路業平上市</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
@@ -4548,34 +4404,33 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下上市</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>通信網路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
@@ -4586,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4598,19 +4453,18 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平上市</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>造紙工業右上上市</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
@@ -4633,19 +4487,18 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上市</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>造紙工業右下上市</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
@@ -4668,21 +4521,20 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上櫃</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>造紙工業平上市</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -4703,19 +4555,18 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>運動休閒右上上市</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
@@ -4738,19 +4589,18 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上櫃</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>運動休閒右上上櫃</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
@@ -4773,19 +4623,18 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上市</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
@@ -4808,19 +4657,18 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>運動休閒右下上櫃</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -4843,19 +4691,18 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上上市</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>運動休閒平上市</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
@@ -4878,19 +4725,18 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下上市</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
@@ -4913,19 +4759,18 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>金融保險右上上市</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
@@ -4948,19 +4793,18 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>金融業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>金融保險右下上市</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
@@ -4971,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4984,18 +4828,17 @@
       </c>
       <c r="J131" t="n">
         <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>金融業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
@@ -5018,19 +4861,18 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>金融業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
@@ -5038,34 +4880,33 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>金融業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
@@ -5073,34 +4914,33 @@
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>金融業平上櫃</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
@@ -5123,89 +4963,86 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>鋼鐵工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
@@ -5218,23 +5055,28 @@
       <c r="F138" t="n">
         <v>0</v>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
       <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>鋼鐵工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
@@ -5242,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5257,19 +5099,18 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -5277,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -5292,19 +5133,18 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>鋼鐵工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
@@ -5315,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5327,24 +5167,23 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>電器電纜右上上市</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -5362,21 +5201,20 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>電器電纜右上上櫃</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -5394,22 +5232,21 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>電器電纜右下上市</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
@@ -5423,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -5432,19 +5269,18 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>電器電纜平上市</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
@@ -5467,21 +5303,20 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>電子通路業右上上市</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -5493,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5502,19 +5337,18 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>電子通路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
@@ -5522,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -5537,19 +5371,18 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>電子通路業右下上市</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -5565,94 +5398,95 @@
       <c r="G148" t="n">
         <v>0</v>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
       <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>2</v>
-      </c>
-      <c r="K149" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>電子通路業平上市</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>2</v>
-      </c>
-      <c r="K150" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>電子通路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -5674,244 +5508,235 @@
       </c>
       <c r="J151" t="n">
         <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>電子零組件業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+          <t>電子零組件業右下上市</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>電子零組件業平上市</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
         <v>2</v>
       </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5920,27 +5745,26 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>電機機械右上上櫃</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -5955,19 +5779,18 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>電機機械右下上市</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
@@ -5990,68 +5813,66 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>電機機械右下上櫃</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+          <t>電機機械平上市</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -6060,16 +5881,13 @@
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電機機械平上櫃</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6088,42 +5906,41 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
-      </c>
-      <c r="K163" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -6132,30 +5949,29 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -6167,27 +5983,26 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -6196,25 +6011,24 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
@@ -6237,19 +6051,18 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -6257,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6272,21 +6085,20 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -6307,19 +6119,18 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
+          <t>食品工業右上上市</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
@@ -6342,57 +6153,176 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
+          <t>食品工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0</v>
+      </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="n">
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" t="n">
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,47 +436,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -487,31 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -524,27 +532,30 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -564,21 +575,24 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -598,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -607,13 +621,16 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -626,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -647,6 +664,9 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -663,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -672,16 +692,19 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -694,28 +717,31 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -725,16 +751,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -743,12 +769,15 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -762,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -783,6 +812,9 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,22 +825,22 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -819,6 +851,9 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -827,16 +862,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -851,6 +886,9 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -864,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -879,12 +917,15 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -895,31 +936,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +973,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -972,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -987,6 +1034,9 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -997,7 +1047,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1021,7 +1071,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1031,10 +1084,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1046,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1055,6 +1108,9 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1065,13 +1121,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1080,15 +1136,18 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1099,31 +1158,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1136,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1145,19 +1207,22 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1193,6 +1258,9 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1204,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1225,6 +1293,9 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1241,24 +1312,27 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1272,16 +1346,16 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1293,6 +1367,9 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1303,30 +1380,33 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
+        <v>9</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1340,29 +1420,32 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>2</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
       </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1374,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1395,6 +1478,9 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1408,27 +1494,30 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1439,13 +1528,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1463,6 +1552,9 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1473,22 +1565,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1497,6 +1589,9 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1507,71 +1602,61 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+          <t>塑膠工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業右下上櫃</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1599,13 +1684,16 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上櫃</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1621,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1633,31 +1721,53 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上市</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>塑膠工業平上市</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
+          <t>塑膠工業平上櫃</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1686,12 +1796,15 @@
       </c>
       <c r="J37" t="n">
         <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
+          <t>居家生活右上上櫃</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1706,26 +1819,25 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
+          <t>居家生活右下上市</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1738,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1753,13 +1865,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
+          <t>居家生活右下上櫃</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1788,12 +1903,15 @@
       </c>
       <c r="J40" t="n">
         <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
+          <t>居家生活平上市</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1814,20 +1932,15 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
+          <t>居家生活平上櫃</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1855,20 +1968,23 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
+          <t>建材營造右上上市</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1890,12 +2006,15 @@
       </c>
       <c r="J43" t="n">
         <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
+          <t>建材營造右上上櫃</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1923,20 +2042,23 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
+          <t>建材營造右下上市</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1958,12 +2080,15 @@
       </c>
       <c r="J45" t="n">
         <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
+          <t>建材營造右下上櫃</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1973,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1982,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1991,13 +2116,16 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
+          <t>建材營造平上市</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2025,17 +2153,20 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
+          <t>建材營造平上櫃</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2059,23 +2190,26 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
+          <t>數位雲端右上上市</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2090,16 +2224,19 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端右上上櫃</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2124,16 +2261,19 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2143,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2161,54 +2301,60 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上櫃</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2220,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2229,13 +2375,16 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>數位雲端平上櫃</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2251,32 +2400,35 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2285,32 +2437,33 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2321,19 +2474,26 @@
       <c r="F56" t="n">
         <v>0</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2361,13 +2521,16 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
+          <t>橡膠工業右上上市</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2395,13 +2558,16 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
+          <t>橡膠工業右下上市</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2429,13 +2595,16 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>橡膠工業平上市</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2456,20 +2625,17 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下上市</t>
+          <t>水泥工業右上上市</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2497,13 +2663,16 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2512,7 +2681,9 @@
       <c r="C62" t="n">
         <v>0</v>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
@@ -2525,20 +2696,27 @@
       <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2547,32 +2725,35 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2587,19 +2768,22 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2618,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2627,20 +2811,23 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -2649,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2661,13 +2848,16 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2677,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2686,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2695,13 +2885,16 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上櫃</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2729,13 +2922,16 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2763,13 +2959,16 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上櫃</t>
+          <t>油電燃氣業平上市</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2793,8 +2992,15 @@
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -2803,22 +3009,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2827,6 +3033,9 @@
         <v>1</v>
       </c>
       <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2863,6 +3072,9 @@
       <c r="J72" t="n">
         <v>0</v>
       </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -2891,8 +3103,15 @@
       <c r="H73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -2901,13 +3120,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2925,6 +3144,9 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2935,31 +3157,34 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
         <v>2</v>
       </c>
-      <c r="E75" t="n">
-        <v>3</v>
-      </c>
       <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>2</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>3</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2975,25 +3200,28 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3012,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3027,7 +3255,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3049,18 +3280,21 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3071,13 +3305,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -3086,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3095,6 +3329,9 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3117,18 +3354,21 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3165,6 +3405,9 @@
       <c r="J81" t="n">
         <v>0</v>
       </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3185,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3197,6 +3440,9 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3233,6 +3479,9 @@
       <c r="J83" t="n">
         <v>0</v>
       </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -3244,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3265,6 +3514,9 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3301,6 +3553,9 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3330,9 +3585,12 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3343,31 +3601,34 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3377,7 +3638,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -3389,19 +3650,22 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3411,19 +3675,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3435,7 +3699,10 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3471,6 +3738,9 @@
       <c r="J90" t="n">
         <v>0</v>
       </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -3494,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3503,6 +3773,9 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3516,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -3528,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3537,6 +3810,9 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3573,6 +3849,9 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -3607,6 +3886,9 @@
       <c r="J94" t="n">
         <v>0</v>
       </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -3641,6 +3923,9 @@
       <c r="J95" t="n">
         <v>0</v>
       </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3648,17 +3933,34 @@
           <t>航運業平上櫃</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3672,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -3693,6 +3995,9 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3729,6 +4034,9 @@
       <c r="J98" t="n">
         <v>0</v>
       </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -3763,6 +4071,9 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -3789,12 +4100,15 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3810,11 +4124,15 @@
       <c r="C101" t="n">
         <v>0</v>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
@@ -3824,7 +4142,12 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -3853,12 +4176,9 @@
       <c r="H102" t="n">
         <v>0</v>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -3867,7 +4187,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -3891,7 +4211,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3927,6 +4250,9 @@
       <c r="J104" t="n">
         <v>0</v>
       </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -3935,13 +4261,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3959,6 +4285,9 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3972,10 +4301,10 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3984,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3994,6 +4323,9 @@
       </c>
       <c r="J106" t="n">
         <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -4003,31 +4335,34 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
         <v>2</v>
       </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
+      <c r="J107" t="n">
         <v>2</v>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
+      <c r="K107" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -4063,6 +4398,9 @@
       <c r="J108" t="n">
         <v>0</v>
       </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -4077,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -4096,6 +4434,9 @@
       </c>
       <c r="J109" t="n">
         <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -4108,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4120,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -4129,6 +4470,9 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4142,28 +4486,31 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -4193,11 +4540,10 @@
       <c r="H112" t="n">
         <v>0</v>
       </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>1</v>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4233,6 +4579,9 @@
       <c r="J113" t="n">
         <v>0</v>
       </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -4240,17 +4589,24 @@
           <t>農業科技業平上櫃</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -4262,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -4271,18 +4627,21 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
       </c>
       <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4293,31 +4652,34 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4327,31 +4689,34 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4364,10 +4729,10 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -4376,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
         <v>1</v>
@@ -4385,6 +4750,9 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
+        <v>2</v>
+      </c>
+      <c r="K118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4404,21 +4772,24 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4432,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -4441,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4453,7 +4824,10 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -4489,6 +4863,9 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -4523,6 +4900,9 @@
       <c r="J122" t="n">
         <v>0</v>
       </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -4557,6 +4937,9 @@
       <c r="J123" t="n">
         <v>0</v>
       </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -4570,12 +4953,8 @@
       <c r="C124" t="n">
         <v>0</v>
       </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>0</v>
       </c>
@@ -4589,6 +4968,9 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4602,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -4623,6 +5005,9 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4639,10 +5024,10 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -4657,6 +5042,9 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4693,6 +5081,9 @@
       <c r="J127" t="n">
         <v>0</v>
       </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -4727,6 +5118,9 @@
       <c r="J128" t="n">
         <v>0</v>
       </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -4758,9 +5152,8 @@
       <c r="I129" t="n">
         <v>0</v>
       </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -4795,6 +5188,9 @@
       <c r="J130" t="n">
         <v>0</v>
       </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -4829,6 +5225,9 @@
       <c r="J131" t="n">
         <v>0</v>
       </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -4863,6 +5262,9 @@
       <c r="J132" t="n">
         <v>0</v>
       </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -4874,13 +5276,13 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4892,9 +5294,12 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4931,11 +5336,14 @@
       <c r="J134" t="n">
         <v>0</v>
       </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>金融業平上櫃</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -4948,96 +5356,105 @@
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
+          <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5065,13 +5482,16 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5099,13 +5519,16 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5133,29 +5556,32 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
+          <t>電器電纜右上上市</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5167,23 +5593,26 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
+          <t>電器電纜右上上櫃</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -5201,20 +5630,23 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -5235,30 +5667,27 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>0</v>
       </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
         <v>0</v>
       </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
         <v>0</v>
       </c>
@@ -5269,17 +5698,20 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電子通路業右上上市</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -5303,13 +5735,16 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
+          <t>電子通路業右上上櫃</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5328,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5337,13 +5772,16 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
+          <t>電子通路業右下上市</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5356,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -5371,20 +5809,23 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
+          <t>電子通路業右下上櫃</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -5402,16 +5843,19 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
+          <t>電子通路業平上市</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5439,13 +5883,16 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
+          <t>電子通路業平上櫃</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5473,128 +5920,140 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
+        <v>12</v>
+      </c>
+      <c r="K151" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業右上上櫃</t>
         </is>
       </c>
       <c r="B152" t="n">
+        <v>10</v>
+      </c>
+      <c r="C152" t="n">
+        <v>8</v>
+      </c>
+      <c r="D152" t="n">
         <v>3</v>
       </c>
-      <c r="C152" t="n">
-        <v>4</v>
-      </c>
-      <c r="D152" t="n">
-        <v>4</v>
-      </c>
       <c r="E152" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
         <v>6</v>
       </c>
-      <c r="G152" t="n">
-        <v>10</v>
-      </c>
       <c r="H152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I152" t="n">
         <v>6</v>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
+          <t>電子零組件業右下上市</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -5606,29 +6065,32 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -5637,72 +6099,78 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
         <v>2</v>
       </c>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" t="n">
-        <v>3</v>
-      </c>
       <c r="F157" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -5711,57 +6179,63 @@
         <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
+          <t>電機機械右上上櫃</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>1</v>
       </c>
       <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
         <v>2</v>
       </c>
-      <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>1</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" t="n">
+      <c r="K158" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -5773,19 +6247,22 @@
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5813,20 +6290,23 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -5847,13 +6327,16 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械平上櫃</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5882,31 +6365,34 @@
       </c>
       <c r="J162" t="n">
         <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
+          <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5916,12 +6402,15 @@
       </c>
       <c r="J163" t="n">
         <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -5931,41 +6420,44 @@
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
         <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>2</v>
       </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>1</v>
@@ -5983,13 +6475,16 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6002,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -6011,23 +6506,26 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
         <v>2</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -6051,26 +6549,29 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6082,16 +6583,19 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>食品工業右上上市</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6119,13 +6623,16 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
+          <t>食品工業右上上櫃</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6153,13 +6660,16 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6187,13 +6697,16 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
+          <t>食品工業右下上櫃</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6221,13 +6734,16 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上市</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -6239,29 +6755,20 @@
       <c r="D173" t="n">
         <v>0</v>
       </c>
-      <c r="E173" t="n">
-        <v>0</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0</v>
-      </c>
-      <c r="H173" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
         <v>0</v>
       </c>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -6291,38 +6798,7 @@
       <c r="J174" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0</v>
-      </c>
-      <c r="H175" t="n">
-        <v>0</v>
-      </c>
-      <c r="I175" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" t="n">
+      <c r="K174" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -492,34 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2" t="n">
         <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -529,33 +521,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -566,19 +555,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -590,9 +579,6 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -612,24 +598,21 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -649,10 +632,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -664,9 +647,6 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -680,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -702,9 +682,6 @@
       </c>
       <c r="J7" t="n">
         <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -740,9 +717,6 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -751,7 +725,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -760,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -775,9 +749,6 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -791,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -812,9 +783,6 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -825,33 +793,30 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -862,16 +827,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -883,12 +848,9 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,30 +864,27 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -936,7 +895,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -948,21 +907,18 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -973,33 +929,30 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1019,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1034,9 +987,6 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1047,7 +997,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1071,9 +1021,6 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1087,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1099,18 +1046,15 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1121,10 +1065,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1145,9 +1089,6 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1158,33 +1099,30 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1201,27 +1139,24 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1258,9 +1193,6 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1290,12 +1222,9 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1332,9 +1261,6 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1369,9 +1295,6 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1380,33 +1303,30 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1417,34 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>17</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1480,9 +1397,6 @@
       <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1494,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1506,18 +1420,15 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1534,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1549,12 +1460,9 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1586,12 +1494,9 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1602,19 +1507,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1623,12 +1528,9 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1642,16 +1544,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1686,9 +1589,6 @@
       <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1723,9 +1623,6 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1760,9 +1657,6 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1786,19 +1680,16 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1807,32 +1698,27 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1867,9 +1753,6 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1893,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1903,9 +1786,6 @@
       </c>
       <c r="J40" t="n">
         <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1920,22 +1800,15 @@
       <c r="C41" t="n">
         <v>0</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1970,9 +1843,6 @@
       <c r="J42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1984,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1996,19 +1866,16 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2044,9 +1911,6 @@
       <c r="J44" t="n">
         <v>0</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -2058,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2070,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2080,9 +1944,6 @@
       </c>
       <c r="J45" t="n">
         <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2095,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2107,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2116,9 +1977,6 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2147,15 +2005,12 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2166,7 +2021,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2190,9 +2045,6 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2215,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2227,10 +2079,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2249,24 +2098,21 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2303,9 +2149,6 @@
       <c r="J51" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -2314,33 +2157,30 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2354,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2366,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2375,9 +2215,6 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2388,33 +2225,30 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2430,11 +2264,9 @@
       <c r="C55" t="n">
         <v>0</v>
       </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2442,14 +2274,13 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2460,10 +2291,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2472,10 +2303,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2484,9 +2315,6 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2523,9 +2351,6 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2560,9 +2385,6 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2597,9 +2419,6 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2613,24 +2432,21 @@
       <c r="C60" t="n">
         <v>0</v>
       </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2665,9 +2481,6 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -2702,9 +2515,6 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2739,9 +2549,6 @@
       <c r="J63" t="n">
         <v>0</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -2753,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2774,9 +2581,6 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2790,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2799,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -2811,10 +2615,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2850,9 +2651,6 @@
       <c r="J66" t="n">
         <v>0</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -2864,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2876,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2885,9 +2683,6 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2924,9 +2719,6 @@
       <c r="J68" t="n">
         <v>0</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -2961,9 +2753,6 @@
       <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -2998,9 +2787,6 @@
       <c r="J70" t="n">
         <v>0</v>
       </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -3012,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3024,18 +2810,15 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3072,9 +2855,6 @@
       <c r="J72" t="n">
         <v>0</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -3109,9 +2889,6 @@
       <c r="J73" t="n">
         <v>0</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -3120,19 +2897,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3141,13 +2918,10 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3157,7 +2931,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -3166,25 +2940,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
         <v>2</v>
       </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3194,16 +2965,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3219,9 +2990,6 @@
       </c>
       <c r="J76" t="n">
         <v>1</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3231,7 +2999,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -3252,13 +3020,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3280,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -3292,9 +3057,6 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3305,10 +3067,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3320,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3329,9 +3091,6 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3368,9 +3127,6 @@
       <c r="J80" t="n">
         <v>0</v>
       </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -3405,9 +3161,6 @@
       <c r="J81" t="n">
         <v>0</v>
       </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3416,7 +3169,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -3428,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3440,9 +3193,6 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3471,15 +3221,12 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3493,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3514,9 +3261,6 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3553,9 +3297,6 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -3590,9 +3331,6 @@
       <c r="J86" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -3601,10 +3339,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -3622,12 +3360,9 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3638,16 +3373,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3656,16 +3391,13 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -3675,10 +3407,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -3690,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3700,9 +3432,6 @@
       </c>
       <c r="J89" t="n">
         <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3733,12 +3462,9 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3775,9 +3501,6 @@
       <c r="J91" t="n">
         <v>0</v>
       </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -3789,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -3810,9 +3533,6 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3849,9 +3569,6 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -3881,12 +3598,9 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3923,9 +3637,6 @@
       <c r="J95" t="n">
         <v>0</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3960,9 +3671,6 @@
       <c r="J96" t="n">
         <v>0</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -3974,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -3995,9 +3703,6 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4034,9 +3739,6 @@
       <c r="J98" t="n">
         <v>0</v>
       </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -4071,9 +3773,6 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -4100,15 +3799,12 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4145,9 +3841,6 @@
       <c r="J101" t="n">
         <v>0</v>
       </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4164,21 +3857,18 @@
       <c r="D102" t="n">
         <v>0</v>
       </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>0</v>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -4187,7 +3877,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -4211,9 +3901,6 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4250,9 +3937,6 @@
       <c r="J104" t="n">
         <v>0</v>
       </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -4261,7 +3945,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -4285,9 +3969,6 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4304,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -4323,9 +4004,6 @@
       </c>
       <c r="J106" t="n">
         <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -4335,25 +4013,25 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I107" t="n">
         <v>2</v>
@@ -4361,9 +4039,6 @@
       <c r="J107" t="n">
         <v>2</v>
       </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -4398,9 +4073,6 @@
       <c r="J108" t="n">
         <v>0</v>
       </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -4415,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -4424,19 +4096,16 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4461,18 +4130,11 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4489,28 +4151,25 @@
         <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
-      </c>
-      <c r="K111" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4528,21 +4187,18 @@
       <c r="D112" t="n">
         <v>0</v>
       </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="n">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4571,15 +4227,12 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4589,24 +4242,19 @@
           <t>農業科技業平上櫃</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -4618,30 +4266,27 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
-      </c>
-      <c r="K115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4652,33 +4297,30 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
         <v>2</v>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
       <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
         <v>2</v>
       </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
       <c r="J116" t="n">
-        <v>2</v>
-      </c>
-      <c r="K116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4689,33 +4331,30 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" t="n">
         <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
         <v>2</v>
       </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
       <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4729,31 +4368,28 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
         <v>2</v>
       </c>
-      <c r="D118" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>2</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -4789,9 +4425,6 @@
       <c r="J119" t="n">
         <v>0</v>
       </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -4803,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -4812,21 +4445,18 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
-      </c>
-      <c r="K120" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4863,9 +4493,6 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -4900,9 +4527,6 @@
       <c r="J122" t="n">
         <v>0</v>
       </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -4937,9 +4561,6 @@
       <c r="J123" t="n">
         <v>0</v>
       </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -4953,8 +4574,12 @@
       <c r="C124" t="n">
         <v>0</v>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
@@ -4968,9 +4593,6 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4984,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -5005,9 +4627,6 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5024,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -5036,15 +4655,12 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5081,9 +4697,6 @@
       <c r="J127" t="n">
         <v>0</v>
       </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -5118,9 +4731,6 @@
       <c r="J128" t="n">
         <v>0</v>
       </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -5140,20 +4750,17 @@
       <c r="E129" t="n">
         <v>0</v>
       </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -5188,9 +4795,6 @@
       <c r="J130" t="n">
         <v>0</v>
       </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -5225,9 +4829,6 @@
       <c r="J131" t="n">
         <v>0</v>
       </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -5262,9 +4863,6 @@
       <c r="J132" t="n">
         <v>0</v>
       </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -5276,13 +4874,13 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -5294,12 +4892,9 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5336,9 +4931,6 @@
       <c r="J134" t="n">
         <v>0</v>
       </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -5347,33 +4939,30 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
-      </c>
-      <c r="K135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5387,19 +4976,19 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -5408,9 +4997,6 @@
         <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
-      </c>
-      <c r="K136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5439,15 +5025,12 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5484,9 +5067,6 @@
       <c r="J138" t="n">
         <v>0</v>
       </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -5521,9 +5101,6 @@
       <c r="J139" t="n">
         <v>0</v>
       </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -5555,12 +5132,7 @@
       <c r="I140" t="n">
         <v>0</v>
       </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -5572,16 +5144,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5593,9 +5165,6 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
-      </c>
-      <c r="K141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5627,12 +5196,9 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5643,7 +5209,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -5667,9 +5233,6 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5679,15 +5242,19 @@
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
@@ -5698,9 +5265,6 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5711,7 +5275,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -5735,9 +5299,6 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5774,9 +5335,6 @@
       <c r="J146" t="n">
         <v>0</v>
       </c>
-      <c r="K146" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -5811,9 +5369,6 @@
       <c r="J147" t="n">
         <v>0</v>
       </c>
-      <c r="K147" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -5822,19 +5377,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -5843,12 +5398,9 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
-      </c>
-      <c r="K148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5885,9 +5437,6 @@
       <c r="J149" t="n">
         <v>0</v>
       </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -5922,9 +5471,6 @@
       <c r="J150" t="n">
         <v>0</v>
       </c>
-      <c r="K150" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -5936,31 +5482,28 @@
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3</v>
+      </c>
+      <c r="F151" t="n">
+        <v>12</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
         <v>2</v>
       </c>
-      <c r="E151" t="n">
-        <v>14</v>
-      </c>
-      <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="n">
-        <v>7</v>
-      </c>
-      <c r="H151" t="n">
-        <v>1</v>
-      </c>
       <c r="I151" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J151" t="n">
-        <v>12</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -5970,34 +5513,31 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D152" t="n">
+        <v>5</v>
+      </c>
+      <c r="E152" t="n">
+        <v>6</v>
+      </c>
+      <c r="F152" t="n">
+        <v>7</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>11</v>
+      </c>
+      <c r="J152" t="n">
         <v>3</v>
-      </c>
-      <c r="E152" t="n">
-        <v>10</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>6</v>
-      </c>
-      <c r="H152" t="n">
-        <v>5</v>
-      </c>
-      <c r="I152" t="n">
-        <v>6</v>
-      </c>
-      <c r="J152" t="n">
-        <v>7</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -6010,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -6025,16 +5565,13 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -6047,13 +5584,13 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -6068,9 +5605,6 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
-      </c>
-      <c r="K154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6081,13 +5615,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -6099,15 +5633,12 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6121,16 +5652,16 @@
         <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -6139,12 +5670,9 @@
         <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
-      </c>
-      <c r="K156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6158,30 +5686,27 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
       </c>
       <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
         <v>2</v>
       </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
       <c r="G157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
-      </c>
-      <c r="K157" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6192,19 +5717,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -6213,13 +5738,10 @@
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -6235,10 +5757,10 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -6247,15 +5769,12 @@
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6278,21 +5797,18 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
-      </c>
-      <c r="K160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6306,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -6327,9 +5843,6 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6355,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -6365,9 +5878,6 @@
       </c>
       <c r="J162" t="n">
         <v>0</v>
-      </c>
-      <c r="K162" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -6377,34 +5887,31 @@
         </is>
       </c>
       <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="n">
+        <v>4</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>4</v>
+      </c>
+      <c r="J163" t="n">
         <v>2</v>
-      </c>
-      <c r="C163" t="n">
-        <v>2</v>
-      </c>
-      <c r="D163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>1</v>
-      </c>
-      <c r="G163" t="n">
-        <v>4</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -6414,34 +5921,31 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>2</v>
-      </c>
-      <c r="K164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -6454,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -6475,9 +5979,6 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6494,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -6503,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -6513,9 +6014,6 @@
       </c>
       <c r="J166" t="n">
         <v>0</v>
-      </c>
-      <c r="K166" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -6551,9 +6049,6 @@
       <c r="J167" t="n">
         <v>0</v>
       </c>
-      <c r="K167" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -6565,13 +6060,13 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6580,15 +6075,12 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" t="n">
         <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6625,9 +6117,6 @@
       <c r="J169" t="n">
         <v>0</v>
       </c>
-      <c r="K169" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -6659,12 +6148,7 @@
       <c r="I170" t="n">
         <v>0</v>
       </c>
-      <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0</v>
-      </c>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -6691,15 +6175,12 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6736,9 +6217,6 @@
       <c r="J172" t="n">
         <v>0</v>
       </c>
-      <c r="K172" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -6746,24 +6224,17 @@
           <t>食品工業平上市</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -6796,9 +6267,6 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
-      </c>
-      <c r="K174" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,47 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17</v>
-      </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -539,10 +539,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -595,22 +595,22 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -632,10 +632,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -740,16 +740,16 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -845,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -895,28 +895,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1105,19 +1105,19 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1148,16 +1148,16 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
       <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>17</v>
-      </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1516,19 +1516,19 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1543,18 +1543,20 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1677,13 +1679,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1698,11 +1700,13 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
@@ -1715,9 +1719,7 @@
       <c r="H38" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1773,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1797,17 +1799,17 @@
       <c r="B41" t="n">
         <v>0</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1863,13 +1865,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -1931,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1953,10 +1955,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2002,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2064,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2095,22 +2097,22 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2157,13 +2159,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2181,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2191,10 +2193,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2234,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2261,12 +2263,12 @@
       <c r="B55" t="n">
         <v>0</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2300,22 +2302,22 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2429,15 +2431,15 @@
       <c r="B60" t="n">
         <v>0</v>
       </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
@@ -2591,22 +2593,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2649,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2659,10 +2661,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -2795,16 +2797,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -2886,9 +2888,7 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -2906,22 +2906,22 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2931,25 +2931,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3033,22 +3033,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -3218,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3376,13 +3376,13 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3394,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3419,10 +3419,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3459,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3796,10 +3796,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -3854,20 +3854,20 @@
       <c r="C102" t="n">
         <v>0</v>
       </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -3991,10 +3991,10 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -4019,25 +4019,25 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
         <v>2</v>
       </c>
       <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" t="n">
         <v>2</v>
-      </c>
-      <c r="G107" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" t="n">
-        <v>4</v>
       </c>
       <c r="I107" t="n">
         <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -4093,16 +4093,16 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4129,11 +4129,11 @@
       <c r="F110" t="n">
         <v>0</v>
       </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
@@ -4145,31 +4145,31 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="n">
         <v>2</v>
       </c>
-      <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" t="n">
-        <v>5</v>
-      </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -4184,11 +4184,11 @@
       <c r="C112" t="n">
         <v>0</v>
       </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
@@ -4224,10 +4224,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -4244,13 +4244,13 @@
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
       <c r="E114" t="n">
         <v>0</v>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -4263,28 +4263,28 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -4297,28 +4297,28 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
         <v>2</v>
       </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
       <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
         <v>2</v>
       </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>1</v>
-      </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -4331,28 +4331,28 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
         <v>2</v>
       </c>
-      <c r="D117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4365,19 +4365,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -4442,22 +4442,22 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4652,10 +4652,10 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
@@ -4889,10 +4889,10 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -4935,33 +4935,17 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
+          <t>金融業平上櫃</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
         <v>0</v>
       </c>
@@ -4969,11 +4953,11 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -4985,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4994,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -5003,20 +4987,20 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
+          <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -5031,13 +5015,13 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5056,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -5071,7 +5055,7 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5105,7 +5089,7 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5132,12 +5116,14 @@
       <c r="I140" t="n">
         <v>0</v>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5153,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5161,9 +5147,7 @@
       <c r="H141" t="n">
         <v>0</v>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
         <v>0</v>
       </c>
@@ -5171,7 +5155,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
+          <t>電器電纜右上上市</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5184,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -5196,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -5205,7 +5189,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜右上上櫃</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5227,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -5239,10 +5223,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>電器電纜右下上市</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
@@ -5271,7 +5257,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -5305,7 +5291,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
+          <t>電子通路業右上上市</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5339,7 +5325,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
+          <t>電子通路業右上上櫃</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5373,7 +5359,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
+          <t>電子通路業右下上市</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5386,10 +5372,10 @@
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -5398,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -5407,7 +5393,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
+          <t>電子通路業右下上櫃</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5417,10 +5403,10 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -5429,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -5441,7 +5427,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
+          <t>電子通路業平上市</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5475,100 +5461,100 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子通路業平上櫃</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F152" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I152" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
+          <t>電子零組件業右上上櫃</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
         <v>1</v>
@@ -5577,7 +5563,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業右下上市</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -5596,13 +5582,13 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -5611,7 +5597,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -5621,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -5636,41 +5622,41 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
         <v>2</v>
       </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="n">
-        <v>1</v>
-      </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
         <v>1</v>
@@ -5679,32 +5665,32 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
         <v>2</v>
       </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>1</v>
-      </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>1</v>
@@ -5713,11 +5699,11 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -5726,16 +5712,16 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I158" t="n">
         <v>1</v>
@@ -5747,48 +5733,48 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右上上櫃</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -5797,16 +5783,16 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -5815,7 +5801,7 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5828,16 +5814,16 @@
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -5849,7 +5835,7 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5868,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5883,45 +5869,45 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電機機械平上櫃</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -5930,19 +5916,19 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>4</v>
+      </c>
+      <c r="I164" t="n">
         <v>2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>2</v>
-      </c>
-      <c r="G164" t="n">
-        <v>1</v>
-      </c>
-      <c r="H164" t="n">
-        <v>2</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -5951,26 +5937,26 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5985,7 +5971,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6004,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -6019,7 +6005,7 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -6035,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -6047,13 +6033,13 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -6066,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -6075,10 +6061,10 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -6087,7 +6073,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6097,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -6106,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -6121,7 +6107,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
+          <t>食品工業右上上市</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6148,12 +6134,14 @@
       <c r="I170" t="n">
         <v>0</v>
       </c>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
+          <t>食品工業右上上櫃</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6175,19 +6163,15 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6206,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -6221,52 +6205,88 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" t="n">
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
         <v>0</v>
       </c>
     </row>
